--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3563-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3563-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2CCCF58-F038-4D4F-920F-FDA1A2DC5B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23F1B4C6-32F0-4076-8D3F-0D31473FDB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4EE3D8B6-9FD8-492F-A4FF-DC5E42A141EB}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{8F048ADA-6E7C-44D9-9102-69FB41344E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="3563-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1558,23 +1558,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42273F3F-CB3F-4654-9F49-CCF93DF3AC8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F371FD-E848-4008-8376-EEE4A47655FB}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1728,7 +1728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1808,7 +1808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>2019</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>27</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>27</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2018</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>2017</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2016</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>2015</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2014</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>2013</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>2012</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="49">
         <v>2011</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51">
         <v>2010</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2009</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="51">
         <v>2008</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
         <v>2007</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51" t="s">
         <v>57</v>
       </c>
